--- a/output/excel/xai_explanation_ITD_2026-08.xlsx
+++ b/output/excel/xai_explanation_ITD_2026-08.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-23 16:09:07</t>
+          <t>2026-08-23 16:21:01</t>
         </is>
       </c>
     </row>
